--- a/Outputs/Scenarios/PtX_demand_MT_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_MT_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000321432175639902</v>
+        <v>0.0003484563351089362</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00053572029273317</v>
+        <v>0.0005060889752501827</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000214288117093268</v>
+        <v>0.0002168952751072212</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.001734884400097794</v>
+        <v>0.001880743452929848</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.002891474000162989</v>
+        <v>0.002731543183177291</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001156589600065196</v>
+        <v>0.001170661364218839</v>
       </c>
     </row>
     <row r="43">
